--- a/sample_data/employees.xlsx
+++ b/sample_data/employees.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>maryam.ahmadi38@company.net</t>
+          <t>maryam.ahmadi38@mail.example</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sofia.ibrahim73@test.org</t>
+          <t>sofia.ibrahim73@example.net</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>david.smith79@company.net</t>
+          <t>david.smith79@mail.example</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -639,7 +639,6 @@
           <t>Chen Rossi</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>sales</t>
@@ -671,7 +670,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>maryam.silva22@company.net</t>
+          <t>maryam.silva22@mail.example</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -705,7 +704,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>david.petrov121@company.net</t>
+          <t>david.petrov121@mail.example</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -721,7 +720,6 @@
           <t>2023-12-11</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="b">
         <v>1</v>
       </c>
@@ -771,7 +769,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mateo.novak56@test.org</t>
+          <t>mateo.novak56@example.net</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -805,7 +803,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>maryam.ahmadi89@mail.com</t>
+          <t>maryam.ahmadi89@example.org</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -832,10 +830,9 @@
       <c r="A13" t="n">
         <v>54</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fatima.novak54@test.org</t>
+          <t>fatima.novak54@example.net</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -869,7 +866,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>david.wang116@company.net</t>
+          <t>david.wang116@mail.example</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -903,7 +900,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>maryam.karimi146@test.org</t>
+          <t>maryam.karimi146@example.net</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -937,7 +934,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ali.muller190@test.org</t>
+          <t>ali.muller190@example.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -971,7 +968,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>maryam.johnson45@company.net</t>
+          <t>maryam.johnson45@mail.example</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1005,7 +1002,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ali.tanaka34@company.net</t>
+          <t>ali.tanaka34@mail.example</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1039,7 +1036,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>yuki.karimi185@mail.com</t>
+          <t>yuki.karimi185@example.org</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1076,7 +1073,6 @@
           <t>reza.novak93@example.com</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>6702.64</v>
       </c>
@@ -1137,7 +1133,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>chen.muller2@test.org</t>
+          <t>chen.muller2@example.net</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1198,10 +1194,9 @@
       <c r="A24" t="n">
         <v>39</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>reza.hosseini39@test.org</t>
+          <t>reza.hosseini39@example.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1235,7 +1230,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nadia.wang77@test.org</t>
+          <t>nadia.wang77@example.net</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1267,7 +1262,6 @@
           <t>Leila Petrov</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>engineering</t>
@@ -1299,7 +1293,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>reza.petrov101@mail.com</t>
+          <t>reza.petrov101@example.org</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1333,7 +1327,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mateo.hosseini150@test.org</t>
+          <t>mateo.hosseini150@example.net</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1365,7 +1359,6 @@
           <t>Lucas Tanaka</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>finance</t>
@@ -1390,7 +1383,6 @@
       <c r="A30" t="n">
         <v>168</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>reza.wang168@example.com</t>
@@ -1427,7 +1419,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>anna.rezaei153@mail.com</t>
+          <t>anna.rezaei153@example.org</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1461,7 +1453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mateo.rossi200@company.net</t>
+          <t>mateo.rossi200@mail.example</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1563,7 +1555,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>leila.ahmadi78@mail.com</t>
+          <t>leila.ahmadi78@example.org</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1574,7 +1566,6 @@
       <c r="E35" t="n">
         <v>2026.98</v>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>67</v>
       </c>
@@ -1627,7 +1618,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ali.wang80@mail.com</t>
+          <t>ali.wang80@example.org</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1661,7 +1652,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>omar.muller1@mail.com</t>
+          <t>omar.muller1@example.org</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1677,7 +1668,6 @@
           <t>2019-12-08</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="b">
         <v>0</v>
       </c>
@@ -1693,7 +1683,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ivan.wang50@mail.com</t>
+          <t>ivan.wang50@example.org</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1727,7 +1717,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nadia.rezaei31@test.org</t>
+          <t>nadia.rezaei31@example.net</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1746,7 +1736,6 @@
       <c r="G40" t="n">
         <v>11</v>
       </c>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1759,7 +1748,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>hassan.novak20@company.net</t>
+          <t>hassan.novak20@mail.example</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1775,7 +1764,6 @@
           <t>2019-09-29</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="b">
         <v>0</v>
       </c>
@@ -1791,7 +1779,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>emma.petrov197@mail.com</t>
+          <t>emma.petrov197@example.org</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1859,7 +1847,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>anna.tanaka3@test.org</t>
+          <t>anna.tanaka3@example.net</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1875,7 +1863,6 @@
           <t>2022-07-03</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="b">
         <v>1</v>
       </c>
@@ -1925,7 +1912,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>hassan.garcia167@mail.com</t>
+          <t>hassan.garcia167@example.org</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1959,7 +1946,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>john.hosseini82@mail.com</t>
+          <t>john.hosseini82@example.org</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1993,7 +1980,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>david.ahmadi41@mail.com</t>
+          <t>david.ahmadi41@example.org</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2012,7 +1999,6 @@
       <c r="G48" t="n">
         <v>24</v>
       </c>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2093,7 +2079,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sara.kowalski35@mail.com</t>
+          <t>sara.kowalski35@example.org</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2195,7 +2181,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ivan.kowalski134@mail.com</t>
+          <t>ivan.kowalski134@example.org</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2229,7 +2215,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>omar.hosseini126@mail.com</t>
+          <t>omar.hosseini126@example.org</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2263,7 +2249,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sara.silva170@company.net</t>
+          <t>sara.silva170@mail.example</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2297,7 +2283,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>reza.wang27@test.org</t>
+          <t>reza.wang27@example.net</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2392,10 +2378,9 @@
       <c r="A60" t="n">
         <v>189</v>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>leila.hosseini189@mail.com</t>
+          <t>leila.hosseini189@example.org</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2432,7 +2417,6 @@
           <t>john.hosseini175@example.com</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
         <v>4063.82</v>
       </c>
@@ -2527,7 +2511,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>nadia.ahmadi18@mail.com</t>
+          <t>nadia.ahmadi18@example.org</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2561,7 +2545,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>leila.muller86@mail.com</t>
+          <t>leila.muller86@example.org</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2595,7 +2579,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sara.garcia157@mail.com</t>
+          <t>sara.garcia157@example.org</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2629,7 +2613,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>david.rossi83@test.org</t>
+          <t>david.rossi83@example.net</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2663,7 +2647,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>leila.wang26@company.net</t>
+          <t>leila.wang26@mail.example</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2697,7 +2681,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>john.wang5@test.org</t>
+          <t>john.wang5@example.net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2731,7 +2715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>anna.petrov118@company.net</t>
+          <t>anna.petrov118@mail.example</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2765,7 +2749,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>mateo.silva99@company.net</t>
+          <t>mateo.silva99@mail.example</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2784,7 +2768,6 @@
       <c r="G71" t="n">
         <v>61</v>
       </c>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2797,7 +2780,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ivan.karimi69@company.net</t>
+          <t>ivan.karimi69@mail.example</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2865,7 +2848,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>john.wang132@test.org</t>
+          <t>john.wang132@example.net</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2918,7 +2901,6 @@
       <c r="G75" t="n">
         <v>5</v>
       </c>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2929,7 +2911,6 @@
           <t>Anna Smith</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>SUPPORT</t>
@@ -2961,7 +2942,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>yuki.johnson15@mail.com</t>
+          <t>yuki.johnson15@example.org</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3029,7 +3010,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>chen.petrov113@mail.com</t>
+          <t>chen.petrov113@example.org</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3097,7 +3078,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>leila.kowalski102@mail.com</t>
+          <t>leila.kowalski102@example.org</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3108,7 +3089,6 @@
       <c r="E81" t="n">
         <v>3433.47</v>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>19</v>
       </c>
@@ -3127,7 +3107,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ivan.ibrahim135@mail.com</t>
+          <t>ivan.ibrahim135@example.org</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3161,7 +3141,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mateo.rossi144@mail.com</t>
+          <t>mateo.rossi144@example.org</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3195,7 +3175,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>yuki.petrov161@test.org</t>
+          <t>yuki.petrov161@example.net</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3229,7 +3209,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>sofia.garcia114@mail.com</t>
+          <t>sofia.garcia114@example.org</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3274,7 +3254,6 @@
       <c r="E86" t="n">
         <v>7542.94</v>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>7</v>
       </c>
@@ -3293,7 +3272,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>chen.wang24@mail.com</t>
+          <t>chen.wang24@example.org</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3301,7 +3280,6 @@
           <t>sales</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>2025-06-10</t>
@@ -3393,7 +3371,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>chen.karimi17@mail.com</t>
+          <t>chen.karimi17@example.org</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3438,7 +3416,6 @@
       <c r="E91" t="n">
         <v>3767.61</v>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
         <v>65</v>
       </c>
@@ -3457,7 +3434,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>sofia.johnson13@company.net</t>
+          <t>sofia.johnson13@mail.example</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3491,7 +3468,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>@nodomain.com</t>
+          <t>@example.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3525,7 +3502,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>lucas.silva100@test.org</t>
+          <t>lucas.silva100@example.net</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3559,7 +3536,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>emma.ibrahim72@test.org</t>
+          <t>emma.ibrahim72@example.net</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3627,7 +3604,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>@nodomain.com</t>
+          <t>@example.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3661,7 +3638,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>hassan.ahmadi76@mail.com</t>
+          <t>hassan.ahmadi76@example.org</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3695,7 +3672,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>david.muller33@company.net</t>
+          <t>david.muller33@mail.example</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3729,7 +3706,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>anna.petrov182@test.org</t>
+          <t>anna.petrov182@example.net</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3797,7 +3774,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>lucas.smith10@company.net</t>
+          <t>lucas.smith10@mail.example</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3831,7 +3808,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>chen.karimi107@mail.com</t>
+          <t>chen.karimi107@example.org</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3865,7 +3842,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>lucas.rezaei84@test.org</t>
+          <t>lucas.rezaei84@example.net</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3899,7 +3876,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>john.ahmadi155@test.org</t>
+          <t>john.ahmadi155@example.net</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3933,7 +3910,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>fatima.smith90@company.net</t>
+          <t>fatima.smith90@mail.example</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4001,7 +3978,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>chen.kowalski52@mail.com</t>
+          <t>chen.kowalski52@example.org</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4035,7 +4012,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ivan.rezaei176@company.net</t>
+          <t>ivan.rezaei176@mail.example</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4103,7 +4080,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>nadia.garcia172@mail.com</t>
+          <t>nadia.garcia172@example.org</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4137,7 +4114,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>lucas.rossi192@company.net</t>
+          <t>lucas.rossi192@mail.example</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4171,7 +4148,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>yuki.johnson85@mail.com</t>
+          <t>yuki.johnson85@example.org</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4205,7 +4182,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>omar.petrov48@test.org</t>
+          <t>omar.petrov48@example.net</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4239,7 +4216,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>elena.kowalski187@test.org</t>
+          <t>elena.kowalski187@example.net</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4273,7 +4250,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>reza.garcia179@company.net</t>
+          <t>reza.garcia179@mail.example</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4341,7 +4318,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>anna.ahmadi4@company.net</t>
+          <t>anna.ahmadi4@mail.example</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4375,7 +4352,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>john.petrov59@test.org</t>
+          <t>john.petrov59@example.net</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4409,7 +4386,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>omar.rossi198@company.net</t>
+          <t>omar.rossi198@mail.example</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4477,7 +4454,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>mateo.johnson143@test.org</t>
+          <t>mateo.johnson143@example.net</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4511,7 +4488,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ivan.rezaei117@mail.com</t>
+          <t>ivan.rezaei117@example.org</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4519,7 +4496,6 @@
           <t>engineering</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>2023-06-24</t>
@@ -4543,7 +4519,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>omar.ibrahim94@company.net</t>
+          <t>omar.ibrahim94@mail.example</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4577,7 +4553,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>maryam.tanaka122@company.net</t>
+          <t>maryam.tanaka122@mail.example</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4596,7 +4572,6 @@
       <c r="G125" t="n">
         <v>86</v>
       </c>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4609,7 +4584,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>david.kowalski105@company.net</t>
+          <t>david.kowalski105@mail.example</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4643,7 +4618,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>sara.smith106@test.org</t>
+          <t>sara.smith106@example.net</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4680,7 +4655,6 @@
           <t>nadia.tanaka21@example.com</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="n">
         <v>3875.42</v>
       </c>
@@ -4707,7 +4681,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>mateo.wang88@test.org</t>
+          <t>mateo.wang88@example.net</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4715,7 +4689,6 @@
           <t>marketing</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>2021-06-28</t>
@@ -4739,7 +4712,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>omar.johnson119@test.org</t>
+          <t>omar.johnson119@example.net</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4807,7 +4780,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>omar.johnson60@company.net</t>
+          <t>omar.johnson60@mail.example</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4841,7 +4814,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>elena.hosseini63@company.net</t>
+          <t>elena.hosseini63@mail.example</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4875,7 +4848,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>emma.hosseini123@company.net</t>
+          <t>emma.hosseini123@mail.example</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4909,7 +4882,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>mateo.hosseini8@mail.com</t>
+          <t>mateo.hosseini8@example.org</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4925,7 +4898,6 @@
           <t>2025-08-16</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="b">
         <v>0</v>
       </c>
@@ -4941,7 +4913,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>yuki.tanaka65@mail.com</t>
+          <t>yuki.tanaka65@example.org</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4975,7 +4947,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>omar.rezaei141@company.net</t>
+          <t>omar.rezaei141@mail.example</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5009,7 +4981,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>anna.ibrahim130@mail.com</t>
+          <t>anna.ibrahim130@example.org</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5043,7 +5015,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>fatima.silva9@mail.com</t>
+          <t>fatima.silva9@example.org</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5077,7 +5049,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>anna.petrov66@mail.com</t>
+          <t>anna.petrov66@example.org</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5111,7 +5083,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>lucas.muller108@mail.com</t>
+          <t>lucas.muller108@example.org</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5145,7 +5117,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>anna.ibrahim46@company.net</t>
+          <t>anna.ibrahim46@mail.example</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5179,7 +5151,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>leila.garcia164@test.org</t>
+          <t>leila.garcia164@example.net</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5213,7 +5185,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>john.garcia152@company.net</t>
+          <t>john.garcia152@mail.example</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5247,7 +5219,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>nadia.rezaei30@company.net</t>
+          <t>nadia.rezaei30@mail.example</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5281,7 +5253,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>leila.wang162@test.org</t>
+          <t>leila.wang162@example.net</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5315,7 +5287,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>maryam.hosseini104@test.org</t>
+          <t>maryam.hosseini104@example.net</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5357,7 +5329,6 @@
           <t>finance</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>2023-04-03</t>
@@ -5415,7 +5386,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>reza.tanaka49@test.org</t>
+          <t>reza.tanaka49@example.net</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5483,7 +5454,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ivan.ibrahim180@test.org</t>
+          <t>ivan.ibrahim180@example.net</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5517,7 +5488,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>leila.karimi23@company.net</t>
+          <t>leila.karimi23@mail.example</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5551,7 +5522,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>sara.petrov44@mail.com</t>
+          <t>sara.petrov44@example.org</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5585,7 +5556,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>lucas.smith10@company.net</t>
+          <t>lucas.smith10@mail.example</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5622,7 +5593,6 @@
           <t>reza.novak93@example.com</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="n">
         <v>6702.64</v>
       </c>
@@ -5649,7 +5619,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>sofia.hosseini142@mail.com</t>
+          <t>sofia.hosseini142@example.org</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5683,7 +5653,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>sara.silva95@mail.com</t>
+          <t>sara.silva95@example.org</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5694,7 +5664,6 @@
       <c r="E158" t="n">
         <v>9058.389999999999</v>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
         <v>59</v>
       </c>
@@ -5713,7 +5682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>david.rezaei136@mail.com</t>
+          <t>david.rezaei136@example.org</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5747,7 +5716,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>reza.rezaei91@test.org</t>
+          <t>reza.rezaei91@example.net</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5781,7 +5750,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>hassan.novak177@mail.com</t>
+          <t>hassan.novak177@example.org</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5815,7 +5784,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>fatima.tanaka19@company.net</t>
+          <t>fatima.tanaka19@mail.example</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5849,7 +5818,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>emma.ibrahim72@test.org</t>
+          <t>emma.ibrahim72@example.net</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5883,7 +5852,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>lucas.silva127@company.net</t>
+          <t>lucas.silva127@mail.example</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5896,7 +5865,6 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
         <v>72</v>
       </c>
@@ -5915,11 +5883,9 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ivan.kowalski149@mail.com</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
+          <t>ivan.kowalski149@example.org</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr">
         <is>
           <t>2019-08-08</t>
@@ -5943,7 +5909,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>omar.ibrahim169@company.net</t>
+          <t>omar.ibrahim169@mail.example</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -6009,7 +5975,6 @@
           <t>Sofia Rossi</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>engineering</t>
@@ -6026,7 +5991,6 @@
       <c r="G168" t="n">
         <v>40</v>
       </c>
-      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6039,7 +6003,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>sara.kowalski133@mail.com</t>
+          <t>sara.kowalski133@example.org</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -6073,7 +6037,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>sara.johnson183@company.net</t>
+          <t>sara.johnson183@mail.example</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -6141,7 +6105,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>nadia.wang158@test.org</t>
+          <t>nadia.wang158@example.net</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -6175,7 +6139,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>sofia.wang70@test.org</t>
+          <t>sofia.wang70@example.net</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -6311,7 +6275,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>hassan.muller151@test.org</t>
+          <t>hassan.muller151@example.net</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -6327,7 +6291,6 @@
           <t>2022-01-04</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="b">
         <v>0</v>
       </c>
@@ -6343,7 +6306,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>hassan.smith98@mail.com</t>
+          <t>hassan.smith98@example.org</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -6445,7 +6408,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>chen.muller103@test.org</t>
+          <t>chen.muller103@example.net</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -6506,7 +6469,6 @@
       <c r="A183" t="n">
         <v>115</v>
       </c>
-      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
           <t>john.ibrahim115@example.com</t>
@@ -6543,7 +6505,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>omar.ahmadi55@mail.com</t>
+          <t>omar.ahmadi55@example.org</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -6579,7 +6541,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>anna.petrov40@test.org</t>
+          <t>anna.petrov40@example.net</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -6681,7 +6643,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>elena.johnson12@test.org</t>
+          <t>elena.johnson12@example.net</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -6697,7 +6659,6 @@
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" t="b">
         <v>1</v>
       </c>
@@ -6711,7 +6672,6 @@
           <t>Sofia Rossi</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>engineering</t>
@@ -6728,7 +6688,6 @@
       <c r="G189" t="n">
         <v>40</v>
       </c>
-      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6741,7 +6700,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>fatima.novak96@test.org</t>
+          <t>fatima.novak96@example.net</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -6775,7 +6734,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>mateo.rezaei111@mail.com</t>
+          <t>mateo.rezaei111@example.org</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6809,10 +6768,9 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>john.ibrahim112@test.org</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
+          <t>john.ibrahim112@example.net</t>
+        </is>
+      </c>
       <c r="E192" t="n">
         <v>9271.959999999999</v>
       </c>
@@ -6839,7 +6797,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>double@@mail.com</t>
+          <t>double@@example.org</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -6915,7 +6873,6 @@
           <t>engineering</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>2024-12-10</t>
@@ -6939,7 +6896,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>john.ibrahim75@test.org</t>
+          <t>john.ibrahim75@example.net</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6973,7 +6930,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>john.johnson61@company.net</t>
+          <t>john.johnson61@mail.example</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -7078,7 +7035,6 @@
           <t>mateo.ibrahim42@example.com</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="n">
         <v>2223.51</v>
       </c>
@@ -7105,7 +7061,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>lucas.muller184@test.org</t>
+          <t>lucas.muller184@example.net</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -7132,10 +7088,9 @@
       <c r="A202" t="n">
         <v>191</v>
       </c>
-      <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
-          <t>david.karimi191@company.net</t>
+          <t>david.karimi191@mail.example</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -7171,7 +7126,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>john.hosseini37@mail.com</t>
+          <t>john.hosseini37@example.org</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -7203,7 +7158,6 @@
           <t>Sofia Wang</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>support</t>
@@ -7235,7 +7189,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>leila.tanaka129@company.net</t>
+          <t>leila.tanaka129@mail.example</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -7269,7 +7223,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>reza.ibrahim97@test.org</t>
+          <t>reza.ibrahim97@example.net</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -7303,7 +7257,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>fatima.smith137@company.net</t>
+          <t>fatima.smith137@mail.example</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
